--- a/generation_zy/hiwo-任务1-1.xlsx
+++ b/generation_zy/hiwo-任务1-1.xlsx
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="10"/>
@@ -778,93 +778,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A02-12</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>B01-FY96</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>240</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A02-12</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B01-FY96</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>320</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A03-96</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>B01-FY96</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>90</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
